--- a/data/trans_bre/IP17-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP17-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-15,62; 2,67</t>
+          <t>-15,11; 3,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,28; 12,95</t>
+          <t>-8,35; 12,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,68; 9,9</t>
+          <t>-9,73; 10,49</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 18,89</t>
+          <t>-0,13; 18,06</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-50,94; 16,57</t>
+          <t>-50,69; 16,55</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-29,5; 75,02</t>
+          <t>-29,85; 69,37</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-36,67; 53,13</t>
+          <t>-34,23; 56,35</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 173,2</t>
+          <t>-3,65; 164,19</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,5; 13,43</t>
+          <t>-6,84; 14,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,34; 18,51</t>
+          <t>0,67; 19,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-11,83; 4,48</t>
+          <t>-13,19; 3,7</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-14,51; 2,02</t>
+          <t>-14,58; 1,74</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-24,94; 73,93</t>
+          <t>-24,15; 83,79</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 139,03</t>
+          <t>2,46; 151,62</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-49,77; 28,75</t>
+          <t>-51,17; 25,48</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-66,91; 18,46</t>
+          <t>-64,63; 18,76</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,89; 7,44</t>
+          <t>-13,01; 6,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,32; 12,96</t>
+          <t>-8,52; 12,5</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,55; 13,18</t>
+          <t>-5,93; 13,48</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-19,78; -1,34</t>
+          <t>-20,36; -1,41</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-53,09; 44,03</t>
+          <t>-54,56; 42,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-28,62; 78,84</t>
+          <t>-32,26; 71,95</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-41,13; 175,37</t>
+          <t>-39,14; 163,34</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-86,99; -0,56</t>
+          <t>-88,75; -1,85</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-11,04; 1,84</t>
+          <t>-11,63; 2,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-9,8; 4,22</t>
+          <t>-9,65; 3,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 8,06</t>
+          <t>-4,68; 8,36</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-12,08; 1,46</t>
+          <t>-12,29; 1,94</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-39,31; 8,81</t>
+          <t>-42,56; 10,67</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-33,27; 19,81</t>
+          <t>-33,08; 16,39</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-18,35; 46,93</t>
+          <t>-20,22; 47,21</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-54,84; 8,17</t>
+          <t>-55,61; 12,39</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,59; 10,9</t>
+          <t>-5,62; 10,83</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,77; 8,74</t>
+          <t>-7,79; 10,18</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,92; 7,58</t>
+          <t>-7,47; 7,99</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,43; 7,59</t>
+          <t>-9,27; 7,47</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-28,26; 81,77</t>
+          <t>-28,32; 82,95</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-30,76; 52,87</t>
+          <t>-28,94; 58,56</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-34,11; 47,35</t>
+          <t>-32,42; 50,96</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-41,56; 53,28</t>
+          <t>-42,65; 49,65</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-22,03; -1,27</t>
+          <t>-21,15; -0,67</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-16,52; 6,88</t>
+          <t>-16,55; 7,47</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-9,11; 13,54</t>
+          <t>-7,64; 14,04</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-13,4; 7,35</t>
+          <t>-12,47; 7,65</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-69,72; -2,94</t>
+          <t>-70,04; -2,8</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-59,86; 43,55</t>
+          <t>-60,15; 44,76</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-44,85; 121,96</t>
+          <t>-39,58; 136,35</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-61,14; 77,19</t>
+          <t>-57,79; 74,78</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,47; 0,54</t>
+          <t>-6,49; 0,7</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 4,67</t>
+          <t>-2,86; 4,51</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 3,85</t>
+          <t>-3,14; 3,93</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,24; 1,24</t>
+          <t>-5,88; 1,31</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-26,53; 2,7</t>
+          <t>-27,37; 3,45</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-12,18; 22,21</t>
+          <t>-12,1; 20,95</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-13,57; 21,62</t>
+          <t>-14,27; 21,53</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-33,31; 7,76</t>
+          <t>-30,1; 8,39</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP17-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP17-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-15,11; 3,28</t>
+          <t>-15,75; 3,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,35; 12,8</t>
+          <t>-8,73; 13,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,73; 10,49</t>
+          <t>-10,54; 9,95</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 18,06</t>
+          <t>-0,12; 18,96</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-50,69; 16,55</t>
+          <t>-51,83; 15,5</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-29,85; 69,37</t>
+          <t>-31,57; 74,09</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-34,23; 56,35</t>
+          <t>-36,01; 55,95</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 164,19</t>
+          <t>-6,37; 161,27</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,84; 14,55</t>
+          <t>-7,74; 14,01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,67; 19,4</t>
+          <t>0,83; 18,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-13,19; 3,7</t>
+          <t>-12,82; 4,31</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-14,58; 1,74</t>
+          <t>-14,81; 2,31</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-24,15; 83,79</t>
+          <t>-27,88; 83,17</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,46; 151,62</t>
+          <t>2,97; 149,16</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-51,17; 25,48</t>
+          <t>-51,68; 29,34</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-64,63; 18,76</t>
+          <t>-67,39; 27,52</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-13,01; 6,37</t>
+          <t>-12,88; 6,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,52; 12,5</t>
+          <t>-8,19; 13,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,93; 13,48</t>
+          <t>-4,92; 13,11</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-20,36; -1,41</t>
+          <t>-20,69; -1,66</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-54,56; 42,01</t>
+          <t>-51,88; 46,19</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-32,26; 71,95</t>
+          <t>-30,82; 76,36</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-39,14; 163,34</t>
+          <t>-33,79; 174,95</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-88,75; -1,85</t>
+          <t>-87,61; -1,37</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-11,63; 2,24</t>
+          <t>-10,82; 1,74</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-9,65; 3,53</t>
+          <t>-10,05; 3,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 8,36</t>
+          <t>-5,43; 7,91</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-12,29; 1,94</t>
+          <t>-12,14; 1,58</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-42,56; 10,67</t>
+          <t>-38,22; 8,81</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-33,08; 16,39</t>
+          <t>-34,75; 15,18</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-20,22; 47,21</t>
+          <t>-22,2; 44,62</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-55,61; 12,39</t>
+          <t>-56,2; 8,92</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,62; 10,83</t>
+          <t>-5,52; 10,12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,79; 10,18</t>
+          <t>-7,0; 9,05</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,47; 7,99</t>
+          <t>-7,22; 8,38</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,27; 7,47</t>
+          <t>-9,7; 7,53</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-28,32; 82,95</t>
+          <t>-27,84; 77,54</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-28,94; 58,56</t>
+          <t>-28,68; 54,17</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-32,42; 50,96</t>
+          <t>-30,92; 50,62</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-42,65; 49,65</t>
+          <t>-42,33; 54,74</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-21,15; -0,67</t>
+          <t>-21,33; -1,22</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-16,55; 7,47</t>
+          <t>-16,8; 7,42</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-7,64; 14,04</t>
+          <t>-8,36; 13,09</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-12,47; 7,65</t>
+          <t>-14,06; 7,63</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-70,04; -2,8</t>
+          <t>-70,23; -6,83</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-60,15; 44,76</t>
+          <t>-60,49; 43,13</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-39,58; 136,35</t>
+          <t>-41,16; 128,46</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-57,79; 74,78</t>
+          <t>-59,97; 75,45</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,49; 0,7</t>
+          <t>-6,81; 0,7</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 4,51</t>
+          <t>-2,98; 4,05</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 3,93</t>
+          <t>-2,71; 4,2</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,88; 1,31</t>
+          <t>-6,32; 1,2</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-27,37; 3,45</t>
+          <t>-27,97; 3,43</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-12,1; 20,95</t>
+          <t>-11,77; 19,17</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-14,27; 21,53</t>
+          <t>-13,54; 22,95</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-30,1; 8,39</t>
+          <t>-32,81; 8,36</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP17-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP17-Clase-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han necesitado consulta del médico en las últimas 2 semanas</t>
+          <t>Menores que han necesitado consulta médica en las últimas 2 semanas</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8,71</t>
+          <t>5,66</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>58,08%</t>
+          <t>36,72%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-15,75; 3,05</t>
+          <t>-15,62; 2,67</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,73; 13,15</t>
+          <t>-8,28; 12,95</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,54; 9,95</t>
+          <t>-10,68; 9,9</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 18,96</t>
+          <t>-3,22; 13,87</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-51,83; 15,5</t>
+          <t>-50,94; 16,57</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-31,57; 74,09</t>
+          <t>-29,5; 75,02</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-36,01; 55,95</t>
+          <t>-36,67; 53,13</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,37; 161,27</t>
+          <t>-15,87; 126,84</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-5,87</t>
+          <t>-6,69</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-34,61%</t>
+          <t>-38,73%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,74; 14,01</t>
+          <t>-7,5; 13,43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,83; 18,89</t>
+          <t>0,34; 18,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-12,82; 4,31</t>
+          <t>-11,83; 4,48</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-14,81; 2,31</t>
+          <t>-15,44; 1,17</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-27,88; 83,17</t>
+          <t>-24,94; 73,93</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,97; 149,16</t>
+          <t>-2,45; 139,03</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-51,68; 29,34</t>
+          <t>-49,77; 28,75</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-67,39; 27,52</t>
+          <t>-69,62; 11,38</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-10,53</t>
+          <t>-11,34</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-61,52%</t>
+          <t>-65,54%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,88; 6,77</t>
+          <t>-12,89; 7,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,19; 13,08</t>
+          <t>-7,32; 12,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 13,11</t>
+          <t>-6,55; 13,18</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-20,69; -1,66</t>
+          <t>-20,62; -2,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-51,88; 46,19</t>
+          <t>-53,09; 44,03</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-30,82; 76,36</t>
+          <t>-28,62; 78,84</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-33,79; 174,95</t>
+          <t>-41,13; 175,37</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-87,61; -1,37</t>
+          <t>-89,06; -8,0</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-4,99</t>
+          <t>-2,52</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-26,48%</t>
+          <t>-13,35%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-10,82; 1,74</t>
+          <t>-11,04; 1,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-10,05; 3,36</t>
+          <t>-9,8; 4,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,43; 7,91</t>
+          <t>-4,55; 8,06</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-12,14; 1,58</t>
+          <t>-8,6; 4,42</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-38,22; 8,81</t>
+          <t>-39,31; 8,81</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-34,75; 15,18</t>
+          <t>-33,27; 19,81</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-22,2; 44,62</t>
+          <t>-18,35; 46,93</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-56,2; 8,92</t>
+          <t>-39,1; 27,75</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-1,27</t>
+          <t>-1,74</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-6,91%</t>
+          <t>-9,41%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,52; 10,12</t>
+          <t>-5,59; 10,9</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,0; 9,05</t>
+          <t>-7,77; 8,74</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,22; 8,38</t>
+          <t>-7,92; 7,58</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,7; 7,53</t>
+          <t>-10,57; 6,31</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-27,84; 77,54</t>
+          <t>-28,26; 81,77</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-28,68; 54,17</t>
+          <t>-30,76; 52,87</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-30,92; 50,62</t>
+          <t>-34,11; 47,35</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-42,33; 54,74</t>
+          <t>-44,55; 43,65</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-2,63</t>
+          <t>-1,74</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-16,22%</t>
+          <t>-11,31%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-21,33; -1,22</t>
+          <t>-22,03; -1,27</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-16,8; 7,42</t>
+          <t>-16,52; 6,88</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-8,36; 13,09</t>
+          <t>-9,11; 13,54</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-14,06; 7,63</t>
+          <t>-11,73; 7,96</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-70,23; -6,83</t>
+          <t>-69,72; -2,94</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-60,49; 43,13</t>
+          <t>-59,86; 43,55</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-41,16; 128,46</t>
+          <t>-44,85; 121,96</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-59,97; 75,45</t>
+          <t>-58,28; 85,76</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-2,39</t>
+          <t>-2,38</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-13,72%</t>
+          <t>-13,58%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,81; 0,7</t>
+          <t>-6,47; 0,54</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 4,05</t>
+          <t>-3,01; 4,67</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 4,2</t>
+          <t>-2,86; 3,85</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,32; 1,2</t>
+          <t>-5,98; 1,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-27,97; 3,43</t>
+          <t>-26,53; 2,7</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-11,77; 19,17</t>
+          <t>-12,18; 22,21</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-13,54; 22,95</t>
+          <t>-13,57; 21,62</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-32,81; 8,36</t>
+          <t>-30,89; 6,63</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP17-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP17-Clase-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-6,37</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1,93</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-0,32</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5,66</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-25,09%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>8,23%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-1,33%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>36,72%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-6.373955229319988</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>1.934881818397324</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-0.3202659528838664</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>5.663895631889429</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.2508652306363079</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.08232213272630474</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-0.013317379704831</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>0.367191349830153</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-15,62; 2,67</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-8,28; 12,95</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-10,68; 9,9</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-3,22; 13,87</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-50,94; 16,57</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-29,5; 75,02</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-36,67; 53,13</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-15,87; 126,84</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-15.62246331544968</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-8.281199732464701</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-10.68253823718306</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-3.220036902873875</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.5093942284593285</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.2950387181562959</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.3667038207374033</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.1586688607587365</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>2.668264684812051</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>12.95178587050642</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>9.897161306770592</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>13.8677789869694</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.1657207738667639</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.7502095547469668</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0.5312571263061909</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>1.268382057517851</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Grupo III</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>3,38</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>9,91</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-4,36</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-6,69</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>14,79%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>59,31%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-21,6%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-38,73%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-7,5; 13,43</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>0,34; 18,51</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-11,83; 4,48</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-15,44; 1,17</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-24,94; 73,93</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-2,45; 139,03</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-49,77; 28,75</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-69,62; 11,38</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>3.384606030747964</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>9.910880534638252</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-4.360593339447</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-6.68624284526181</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.1479055250261108</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.5930732933321231</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.2159533134250273</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.3872995786528395</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Grupo IV y V</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-3,4</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>2,69</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>3,79</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-11,34</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-16,87%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>12,27%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>31,03%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-65,54%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-7.50020004616042</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.3438469185494653</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-11.8294003452331</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-15.4434583772587</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.2493582637690589</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.02448698326261029</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.4977235220639613</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.6962034596137614</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-12,89; 7,44</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-7,32; 12,96</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-6,55; 13,18</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-20,62; -2,0</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-53,09; 44,03</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-28,62; 78,84</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-41,13; 175,37</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-89,06; -8,0</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>13.43072509350173</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>18.5050378532664</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>4.481140468200056</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>1.167240325999217</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.7392884435992161</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>1.390336681491256</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.287484360012548</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.1137785024508841</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Grupo VI</t>
+          <t>Grupo IV y V</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,299 +819,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-4,61</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-2,95</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1,65</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-2,52</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-19,0%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-11,46%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>7,85%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-13,35%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-3.401898099466261</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>2.690686074176754</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>3.793355134948745</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-11.34026819532444</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.1686946984101918</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.1227061716389666</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0.3103189621954453</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.6554223284737649</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-11,04; 1,84</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-9,8; 4,22</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-4,55; 8,06</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-8,6; 4,42</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-39,31; 8,81</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-33,27; 19,81</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-18,35; 46,93</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-39,1; 27,75</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-12.89477173452464</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-7.32438255998795</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-6.54984359556197</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-20.61792018947443</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.5309437673125853</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.2862101732159479</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.4112719666962203</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.8905681509986788</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Grupo VII</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>7.435591054088968</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>12.95619507292157</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>13.18442691850578</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>-1.996551994601372</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.4403090158188753</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.7883989861656667</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>1.753678780416594</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>-0.08002928884368829</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>2,52</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>0,9</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,19</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-1,74</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>14,95%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>4,21%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-9,41%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-5,59; 10,9</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-7,77; 8,74</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-7,92; 7,58</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-10,57; 6,31</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-28,26; 81,77</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-30,76; 52,87</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-34,11; 47,35</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-44,55; 43,65</t>
-        </is>
+      <c r="C13" s="5" t="n">
+        <v>-4.607229103608673</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-2.946873388769017</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>1.649291812643078</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-2.522319528664271</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.1900390137265564</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.1146025197732781</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.07848362044339099</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.1334808026006903</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>No ha trabajado</t>
-        </is>
-      </c>
+      <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>-11,34</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>-4,88</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>2,54</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-1,74</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-44,9%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-21,48%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>16,44%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>-11,31%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-11.03675092207306</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-9.797293968246636</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-4.549304897410988</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-8.599355125577347</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.3931151522364895</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.3326753894581566</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.1834983684484136</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.3909942616336021</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>-22,03; -1,27</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>-16,52; 6,88</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>-9,11; 13,54</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>-11,73; 7,96</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>-69,72; -2,94</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-59,86; 43,55</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>-44,85; 121,96</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>-58,28; 85,76</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>1.838038964900646</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>4.217268518258887</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>8.058960817805694</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>4.422187510091184</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.08813425980338829</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.1981041655244833</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.4692839243879272</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.2775074896201469</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Grupo VII</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1210,97 +1019,297 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>-2,95</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>0,78</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,54</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-2,38</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-13,19%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>3,43%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2,77%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>-13,58%</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>2.51572887204442</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.9024885041549885</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.1850521107052222</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-1.742271485318017</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0.1495294573660142</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.0421110307808603</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>0.009325290159001177</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>-0.09409393937517015</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-6,47; 0,54</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-3,01; 4,67</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-2,86; 3,85</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-5,98; 1,0</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-26,53; 2,7</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-12,18; 22,21</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-13,57; 21,62</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-30,89; 6,63</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-5.58593387506856</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-7.771109881691711</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-7.921060155913212</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-10.57220636121347</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.2825588371595222</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.3076132884620186</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.3411274686084182</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.4454594627000336</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>10.896069143055</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>8.741207609176021</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>7.583486552579193</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>6.314942383298051</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.8176915497198447</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.5286869835383597</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.4735351334017697</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.4365469558919921</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>-11.33579255947062</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>-4.88263403749348</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>2.540323232730204</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>-1.73673232473282</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>-0.4489982596910821</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-0.214761166755895</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>0.1643820687490339</v>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>-0.1130510660142044</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>-22.0338664307797</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>-16.51778731755618</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>-9.107123788712492</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>-11.73409625171093</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-0.6971712826606423</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>-0.5985909484676908</v>
+      </c>
+      <c r="I20" s="6" t="n">
+        <v>-0.4484979141806515</v>
+      </c>
+      <c r="J20" s="6" t="n">
+        <v>-0.582784425739199</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>-1.266235153241692</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>6.87888972345799</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>13.53634264538042</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>7.9572620369573</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>-0.029440116476142</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>0.4355460529797395</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>1.219610098038428</v>
+      </c>
+      <c r="J21" s="6" t="n">
+        <v>0.8576342996720883</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>-2.950809643595001</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>0.77633689172045</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>0.5419745350149968</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>-2.376830606430747</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>-0.1318875777724695</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>0.03432171109209115</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>0.0276505038799417</v>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>-0.1358245824971269</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-6.472358999826233</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-3.011742459623475</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-2.859514617401668</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-5.980423982835351</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>-0.2652842519136824</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>-0.1217828411759867</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>-0.1356782577501748</v>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>-0.3089298221415298</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>0.5362681344996715</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>4.672799873312548</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>3.846413007081734</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>0.9988920003794727</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>0.0269717121277617</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>0.2221384558463387</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>0.2162458941885947</v>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>0.06626327118380659</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1308,16 +1317,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
